--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,6 +2657,322 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121561246</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>625158</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7209781</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121561245</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625079</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7209811</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121561247</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625210</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7209708</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B19" t="n">
         <v>57355</v>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B21" t="n">
         <v>57355</v>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R21" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561245</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2800,16 +2800,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625079</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209811</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2889,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,21 +2907,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R21" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,7 +2659,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561246</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625158</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561247</v>
+        <v>121561245</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625210</v>
+        <v>625079</v>
       </c>
       <c r="R19" t="n">
-        <v>7209708</v>
+        <v>7209811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2873,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561245</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2907,16 +2902,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625079</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209811</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561245</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,16 +2693,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625079</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209811</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>121561245</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2795,21 +2800,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625079</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2766,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561245</v>
+        <v>121561246</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2782,16 +2777,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2800,16 +2795,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625079</v>
+        <v>625158</v>
       </c>
       <c r="R20" t="n">
-        <v>7209811</v>
+        <v>7209781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561245</v>
+        <v>121561246</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,16 +2693,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625079</v>
+        <v>625158</v>
       </c>
       <c r="R19" t="n">
-        <v>7209811</v>
+        <v>7209781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,7 +2766,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561246</v>
+        <v>121561247</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2806,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625158</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209781</v>
+        <v>7209708</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561247</v>
+        <v>121561245</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,16 +2889,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,21 +2907,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625079</v>
       </c>
       <c r="R21" t="n">
-        <v>7209708</v>
+        <v>7209811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -2659,10 +2659,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561246</v>
+        <v>121561245</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,16 +2675,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2693,21 +2693,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625158</v>
+        <v>625079</v>
       </c>
       <c r="R19" t="n">
-        <v>7209781</v>
+        <v>7209811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2873,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561245</v>
+        <v>121561246</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,16 +2884,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2907,16 +2902,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625079</v>
+        <v>625158</v>
       </c>
       <c r="R21" t="n">
-        <v>7209811</v>
+        <v>7209781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60880-2023 artfynd.xlsx
+++ b/artfynd/A 60880-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111336414</v>
+        <v>121561245</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625154.518985283</v>
+        <v>625079</v>
       </c>
       <c r="R2" t="n">
-        <v>7209790.550712772</v>
+        <v>7209811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,54 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111336410</v>
+        <v>121561246</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625259.9138955096</v>
+        <v>625158</v>
       </c>
       <c r="R3" t="n">
-        <v>7209755.994336623</v>
+        <v>7209781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +856,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,54 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111336409</v>
+        <v>121561247</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625220.7730415409</v>
+        <v>625210</v>
       </c>
       <c r="R4" t="n">
-        <v>7209758.586850428</v>
+        <v>7209708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +958,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,54 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111336412</v>
+        <v>121561248</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625184.8249035137</v>
+        <v>625169</v>
       </c>
       <c r="R5" t="n">
-        <v>7209765.975211025</v>
+        <v>7209699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1055,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111336416</v>
+        <v>111336397</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625105.0111505401</v>
+        <v>625081</v>
       </c>
       <c r="R6" t="n">
-        <v>7209827.879692691</v>
+        <v>7209864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,19 +1145,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111336408</v>
+        <v>111336400</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625192.9989858982</v>
+        <v>625049</v>
       </c>
       <c r="R7" t="n">
-        <v>7209753.182408583</v>
+        <v>7209829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,19 +1247,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111336403</v>
+        <v>111336402</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625077.0981605061</v>
+        <v>625059</v>
       </c>
       <c r="R8" t="n">
-        <v>7209815.690764531</v>
+        <v>7209824</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,19 +1349,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111336413</v>
+        <v>111336403</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625162.5685057295</v>
+        <v>625077</v>
       </c>
       <c r="R9" t="n">
-        <v>7209780.71893465</v>
+        <v>7209816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,19 +1451,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,15 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111336407</v>
+        <v>111336404</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625184.0874587877</v>
+        <v>625134</v>
       </c>
       <c r="R10" t="n">
-        <v>7209753.231787121</v>
+        <v>7209755</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,19 +1553,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111336404</v>
+        <v>111336405</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625133.9709027896</v>
+        <v>625164</v>
       </c>
       <c r="R11" t="n">
-        <v>7209754.516890368</v>
+        <v>7209748</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,19 +1655,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111336398</v>
+        <v>111336406</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625080.5973707421</v>
+        <v>625199</v>
       </c>
       <c r="R12" t="n">
-        <v>7209863.719748351</v>
+        <v>7209682</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,19 +1757,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,15 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111336419</v>
+        <v>111336407</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625180.6727454782</v>
+        <v>625184</v>
       </c>
       <c r="R13" t="n">
-        <v>7209784.021863313</v>
+        <v>7209753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,19 +1859,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,15 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111336417</v>
+        <v>111336408</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625114.8910281583</v>
+        <v>625193</v>
       </c>
       <c r="R14" t="n">
-        <v>7209835.074288641</v>
+        <v>7209754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,19 +1961,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,15 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111336411</v>
+        <v>111336409</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625220.1037653659</v>
+        <v>625221</v>
       </c>
       <c r="R15" t="n">
-        <v>7209754.321236268</v>
+        <v>7209758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2273,19 +2063,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,15 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111336415</v>
+        <v>111336410</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625148.1990682605</v>
+        <v>625259</v>
       </c>
       <c r="R16" t="n">
-        <v>7209799.60762905</v>
+        <v>7209756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2390,19 +2165,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,15 +2195,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111336405</v>
+        <v>111336411</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625163.9543035047</v>
+        <v>625220</v>
       </c>
       <c r="R17" t="n">
-        <v>7209747.724855823</v>
+        <v>7209755</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,19 +2267,9 @@
           <t>2023-08-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,15 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111396307</v>
+        <v>111336412</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2581,16 +2326,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625152.9229681741</v>
+        <v>625185</v>
       </c>
       <c r="R18" t="n">
-        <v>7209818.450615434</v>
+        <v>7209766</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2617,22 +2366,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,6 +2380,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2659,50 +2399,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121561245</v>
+        <v>111336413</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625079</v>
+        <v>625163</v>
       </c>
       <c r="R19" t="n">
-        <v>7209811</v>
+        <v>7209780</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,12 +2468,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,6 +2482,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2761,55 +2501,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561247</v>
+        <v>111336414</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625154</v>
       </c>
       <c r="R20" t="n">
-        <v>7209708</v>
+        <v>7209791</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,12 +2570,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,6 +2584,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2868,55 +2603,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561246</v>
+        <v>111336415</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625158</v>
+        <v>625148</v>
       </c>
       <c r="R21" t="n">
-        <v>7209781</v>
+        <v>7209800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,12 +2672,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,6 +2686,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2972,6 +2702,409 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111336416</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625105</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7209828</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111336417</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>625114</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7209835</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111336419</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>625181</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7209784</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111396307</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>625153</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7209819</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
